--- a/important_mails_2026-07-22.xlsx
+++ b/important_mails_2026-07-22.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -533,12 +533,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -548,21 +548,122 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
+          <t>Wed, 22 Jul 2026 14:43:36 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 07/22/26 14:43 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 291.50.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 14:42:48 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 07/22/26 14:42 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 1.058,86.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -578,39 +679,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 04:57:37 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -626,39 +727,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 14:04:25 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -679,39 +780,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 04:59:54 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -727,39 +828,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 14:58:02 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -780,39 +881,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 05:03:59 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -828,39 +929,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 05:02:32 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -876,39 +977,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 08:07:04 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -925,39 +1026,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 07:52:22 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -995,39 +1096,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:31:05 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -1044,39 +1145,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:30:30 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -1114,39 +1215,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 16:00:40 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -1163,39 +1264,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 15:59:18 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -1233,39 +1334,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 07:44:38 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -1282,40 +1383,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 07:43:19 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -1330,39 +1431,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 13:57:14 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1382,39 +1483,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 15:31:53 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1434,39 +1535,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 15:31:22 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1486,39 +1587,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 15:30:38 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1535,88 +1636,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 14:47:49 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 07/15/26 14:47 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 925,70.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 12:36:12 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1632,39 +1684,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 13:53:00 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1679,39 +1731,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 11:19:50 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution’s new China shipping options are live</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Choose Shanghai or Shenzhen with Free on Board support
@@ -1726,60 +1778,10 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo]
-We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
-[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-all-ref--xx-invmgr-dnav-xx/7z4njtm/6769022163/h/8vIvt897JI4FIoN1zpbOfGsnK8r65MNsf-5hLns08l0)
-We've improved our Similar Item Pricing tool designed specifically to help you make faster, more informed pricing decisions.
-Here’s what’s new:
-Browse Amazon-highlighted similar products based on your catalog or search for specific products yourself
-Access key data points including Delivery Experience, Prime Status, Product Ratings, and more
-Ready to get started? It's simple:
-- Go to your 'Manage All Inventory'
-- Click on 'View Reference Prices' in the Pricing column
-- Select 'Set Up Similar Products' to access the dashboard
-The Similar Items Dashboard can help you research prices for products customers may see as comparable to yours and make more informed pricing decision.
-[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-al</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1794,68 +1796,21 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
+          <t>Sat, 18 Jul 2026 04:29:33 +0000</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Get increased New Selection Program (2026) benefits starting July
- 30</t>
+          <t>Create FBA removal order by 2026-07-30</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>96
- Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
- Hello,
- If you’re currently enrolled in our existing New Selection Program , you’ll automatically receive New Selection Program (2026) benefits for new branded FBA ASINs that launch starting July 30, through October 31, 2026, as an introductory offer.
- To continue to receive New Selection Program (2026) benefits after October 31, you must confirm your enrollment on Enroll in New Selection Program (2026) . From July 30, the existing New Selection Program will end.
-New benefits for an eligible new-to-FBA product include (applicable from first inventory received date):
-- Instant fee credits equivalent to capping referral fees to 10% (or your existing rate, whichever is lower) on your first 100 units and 5% (or your existing rate, whichever is lower) on the next 100 units. Credits apply to major fees, like referral and fulfillment fees.
-- $50 in coupon variable fee credits and $75 in Vine enrollment fee credits (applied to middle tier), usable within the first 60 days.
-- Free storage, free c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 18 Jul 2026 04:29:33 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-07-30</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1878,39 +1833,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 04:12:27 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1935,39 +1890,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 03:41:39 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1990,39 +1945,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 05:44:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">【重要】西班牙VAT通知期延期指南。税号激活用时最长达37周，请立即行动以免影响销售 </t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>西班牙延期政策更新：已过通知期也可发起申请
 			尊敬的 深圳市微海众信科技有限公司,
@@ -2058,39 +2013,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
@@ -2102,39 +2057,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 04:56:43 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2150,39 +2105,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:08:13 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2203,39 +2158,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 04:45:43 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2251,39 +2206,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 14:23:23 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $88.37 in an attempt to settle your Amazon seller account balance.
@@ -2299,39 +2254,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 09:58:04 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2347,39 +2302,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 05:37:52 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2395,39 +2350,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2443,39 +2398,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2491,39 +2446,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0uWEj59btv)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2543,39 +2498,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2591,39 +2546,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 09:21:14 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2639,39 +2594,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 09:24:36 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2687,39 +2642,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 04:17:03 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (go0BbIMUoR)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2739,39 +2694,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:27:45 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hbXn1jQJTV)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2796,39 +2751,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 05:07:37 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2844,39 +2799,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 08:53:34 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2cKowrwuw)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2896,39 +2851,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:56:23 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2944,39 +2899,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 23:44:37 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (H7OQM8penQ)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3001,39 +2956,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 04:56:45 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3049,39 +3004,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3102,39 +3057,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
@@ -3150,39 +3105,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 04:47:15 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3198,39 +3153,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 04:59:26 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3246,39 +3201,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 03:07:14 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (HI24ImSBWG)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3303,39 +3258,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 15:41:57 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3356,39 +3311,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 09:07:47 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -3402,39 +3357,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 04:53:58 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3450,39 +3405,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 00:27:04 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FyqS0yVk5B)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3507,39 +3462,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:45:26 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3555,39 +3510,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 15:11:41 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3608,39 +3563,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:24:45 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (1M28ecQsao)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3665,39 +3620,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 06:20:20 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (9U/Ti42WHq)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3717,39 +3672,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 04:45:03 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3765,39 +3720,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -3830,39 +3785,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -3879,40 +3834,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -3927,39 +3882,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -3973,6 +3928,55 @@
  We’re here to help.
  If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
  For more informa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 14:47:49 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 07/15/26 14:47 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 925,70.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
         </is>
       </c>
     </row>
@@ -7092,21 +7096,118 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
+          <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Worten Marketplace - Portugal y España</t>
+          <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo]
+We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
+[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-all-ref--xx-invmgr-dnav-xx/7z4njtm/6769022163/h/8vIvt897JI4FIoN1zpbOfGsnK8r65MNsf-5hLns08l0)
+We've improved our Similar Item Pricing tool designed specifically to help you make faster, more informed pricing decisions.
+Here’s what’s new:
+Browse Amazon-highlighted similar products based on your catalog or search for specific products yourself
+Access key data points including Delivery Experience, Prime Status, Product Ratings, and more
+Ready to get started? It's simple:
+- Go to your 'Manage All Inventory'
+- Click on 'View Reference Prices' in the Pricing column
+- Select 'Set Up Similar Products' to access the dashboard
+The Similar Items Dashboard can help you research prices for products customers may see as comparable to yours and make more informed pricing decision.
+[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-al</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Get increased New Selection Program (2026) benefits starting July
+ 30</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
+ Hello,
+ If you’re currently enrolled in our existing New Selection Program , you’ll automatically receive New Selection Program (2026) benefits for new branded FBA ASINs that launch starting July 30, through October 31, 2026, as an introductory offer.
+ To continue to receive New Selection Program (2026) benefits after October 31, you must confirm your enrollment on Enroll in New Selection Program (2026) . From July 30, the existing New Selection Program will end.
+New benefits for an eligible new-to-FBA product include (applicable from first inventory received date):
+- Instant fee credits equivalent to capping referral fees to 10% (or your existing rate, whichever is lower) on your first 100 units and 5% (or your existing rate, whichever is lower) on the next 100 units. Credits apply to major fees, like referral and fulfillment fees.
+- $50 in coupon variable fee credits and $75 in Vine enrollment fee credits (applied to middle tier), usable within the first 60 days.
+- Free storage, free c</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7122,40 +7223,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 22:17:55 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for
  6/2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for 6/2026
  96
@@ -7177,39 +7278,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:24:05 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -7231,39 +7332,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:47 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7278,40 +7379,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 23:30:27 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -7329,39 +7430,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 20:04:53 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -7380,39 +7481,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 15:47:06 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -7430,39 +7531,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 14:10:23 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7480,39 +7581,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:46:14 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -7531,39 +7632,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 10:28:11 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7582,39 +7683,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 09:08:55 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -7633,39 +7734,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 08:53:55 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -7703,40 +7804,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 20:45:55 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -7754,39 +7855,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 18:16:40 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -7805,39 +7906,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 14:45:21 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -7855,39 +7956,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 12:00:55 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -7906,39 +8007,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:53:57 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7957,39 +8058,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:08:27 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -8008,39 +8109,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:12 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026
  96
@@ -8058,39 +8159,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:22:50 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026
  96
@@ -8114,39 +8215,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:18:37 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026
  96
@@ -8173,39 +8274,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:58:57 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -8232,39 +8333,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:24:51 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -8287,39 +8388,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:10:44 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026
  96
@@ -8343,39 +8444,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:00:23 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026
  96
@@ -8402,39 +8503,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:41:16 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -8461,39 +8562,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:20:20 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026
  96
@@ -8513,39 +8614,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:05:26 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -8568,39 +8669,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:01:10 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -8625,39 +8726,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:33:27 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -8676,39 +8777,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:22:23 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026
  96
@@ -8726,39 +8827,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:13:46 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -8783,39 +8884,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 23:07:09 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -8834,39 +8935,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:44:31 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -8891,39 +8992,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:29:53 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026
  96
@@ -8948,39 +9049,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:23:16 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -8999,39 +9100,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:07:51 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -9058,39 +9159,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:56:46 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9117,39 +9218,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:36:00 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -9174,39 +9275,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:27:56 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026
  96
@@ -9233,39 +9334,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:23:50 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -9289,39 +9390,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026
  96
@@ -9348,39 +9449,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:02:23 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -9407,39 +9508,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:58:54 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9466,39 +9567,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:55:57 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026
  96
@@ -9523,39 +9624,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:16:22 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9582,39 +9683,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:05:55 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026
  96
@@ -9639,39 +9740,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:55:02 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -9689,39 +9790,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:14:51 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -9745,39 +9846,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:47:27 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -9804,39 +9905,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:46:42 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026
  96
@@ -9854,39 +9955,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:31:36 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -9911,39 +10012,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:28:53 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -9961,39 +10062,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:10:41 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10017,39 +10118,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:01:49 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -10067,39 +10168,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:42:42 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026
  96
@@ -10117,39 +10218,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:21:50 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -10176,39 +10277,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:02:53 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -10233,40 +10334,40 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:46:03 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk
  sales</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk sales
  96
@@ -10281,39 +10382,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:40:18 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026
  96
@@ -10334,39 +10435,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10390,39 +10491,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:30:53 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -10440,39 +10541,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 14:51:08 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026
  96
@@ -10495,39 +10596,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 13:53:08 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10542,39 +10643,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 12:49:39 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -10589,39 +10690,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:26:45 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>El Asistente de vendedores ya está activo en Francia, Italia y España</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  La asistencia con tecnología de IA ya está disponible en Seller Central para ayudarte a gestionar tu negocio de forma más eficiente.
@@ -10635,39 +10736,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:11:01 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -10685,39 +10786,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 13:49:18 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>L'assistente venditori è ora attivo in Francia, Italia e Spagna</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  L'assistenza basata su AI è ora disponibile in Seller Central per aiutarti a gestire la tua attività in modo più efficiente.
@@ -10732,39 +10833,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:04:35 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -10781,39 +10882,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 02:53:05 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 06/2026</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -10831,39 +10932,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 00:26:34 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;
@@ -10878,39 +10979,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:10:24 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -10926,39 +11027,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10973,39 +11074,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -11033,39 +11134,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -11094,39 +11195,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -11144,39 +11245,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11195,39 +11296,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -11241,39 +11342,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -11288,39 +11389,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -11344,39 +11445,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11397,39 +11498,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11452,39 +11553,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11507,39 +11608,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11563,39 +11664,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:35:02 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11618,39 +11719,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:23:13 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11671,39 +11772,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11727,39 +11828,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11783,39 +11884,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11837,39 +11938,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Your Accelerate 2026 session catalog is now live</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
@@ -11881,40 +11982,40 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 03:21:27 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>[Amazon.co.uk] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.co.uk] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -11931,39 +12032,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -11993,39 +12094,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
